--- a/网站内容_英文.xlsx
+++ b/网站内容_英文.xlsx
@@ -1,56 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Homepage" sheetId="1" r:id="rId1"/>
-    <sheet name="Research Area 1" sheetId="2" r:id="rId2"/>
-    <sheet name="Research Area 2" sheetId="3" r:id="rId3"/>
-    <sheet name="Data &amp; Model" sheetId="4" r:id="rId4"/>
-    <sheet name="Platform" sheetId="5" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Homepage" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Area 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Area 2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data &amp; Model" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -69,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -400,229 +444,270 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Basic Information</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Research Areas:</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Education</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Publication</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Project</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Course</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Student</v>
-      </c>
-    </row>
-    <row r="2" xml:space="preserve">
-      <c r="A2" t="str" xml:space="preserve">
-        <v xml:space="preserve">[Name], [Title], [Affiliation]
-Advisor: \href{https://example.com}{Prof. [Advisor Name]}</v>
-      </c>
-      <c r="B2" t="str">
-        <v>[Area 1]: [Description]</v>
-      </c>
-      <c r="C2" t="str">
-        <v>[Period], [University], [Department], Ph.D.</v>
-      </c>
-      <c r="D2" t="str">
-        <v>\textbf{[Name]}, [Paper Title], [Journal/Conference], [Year]</v>
-      </c>
-      <c r="E2" t="str">
-        <v>[Project Name], [Funding Source], [Role]</v>
-      </c>
-      <c r="F2" t="str">
-        <v>[Course Name], [Year]</v>
-      </c>
-      <c r="G2" t="str">
-        <v>[Recruiting/Team Info]</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Basic Information</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Research Areas:</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Course</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Desheng, Undergraduate, School of Foreign Languages, Shanghai Jiao Tong University</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Contrastive Linguistics: Japanese-Chinese contrastive research across phonological, lexical, and syntactic levels</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2022–Present, Shanghai Jiao Tong University, School of Foreign Languages, B.A.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Research on Script and Language Exchange in the Chinese Character Cultural Sphere, PRP Undergraduate Research Program, Participant (Supervisor: Prof. Li Siqi)</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>photo.jpg</v>
-      </c>
-      <c r="B3" t="str">
-        <v>[Area 2]: [Description]</v>
-      </c>
-      <c r="C3" t="str">
-        <v>[Period], [University], [Department], M.A.</v>
-      </c>
-      <c r="D3" t="str">
-        <v>\textbf{[Name]}, [Paper Title 2], [Journal/Conference], [Year]</v>
-      </c>
-      <c r="E3" t="str">
-        <v>[Project Name 2], [Funding Source]</v>
-      </c>
-      <c r="F3" t="str">
-        <v>[Course Name 2], [Year]</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v/>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v>[Period], [University], [Major], B.A.</v>
-      </c>
-      <c r="D4" t="str">
-        <v>\textbf{[Name]}, [Paper Title 3], [Journal/Conference], [Year]</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-    </row>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>photo.jpg</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cognitive Semantics: Media corpus research based on cognitive critical discourse analysis</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sep 2025–Feb 2026, Osaka University, School of Foreign Studies, Exchange Student</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>[Research Area 1 Title]</v>
-      </c>
-      <c r="B1" t="str">
-        <v>[Subtopic A]</v>
-      </c>
-      <c r="C1" t="str">
-        <v>[Subtopic B]</v>
-      </c>
-    </row>
-    <row r="2" xml:space="preserve">
-      <c r="A2" t="str">
-        <v>[Detailed description, use \textbf{bold} and \href{url}{links}]</v>
-      </c>
-      <c r="B2" t="str" xml:space="preserve">
-        <v xml:space="preserve">[Subtopic A description]
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>[Research Area 1 Title]</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>[Subtopic A]</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>[Subtopic B]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>[Detailed description, use \textbf{bold} and \href{url}{links}]</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[Subtopic A description]
 &gt;[Point 1]
-&gt;[Point 2]</v>
-      </c>
-      <c r="C2" t="str">
-        <v>[Subtopic B description, \textit{italic reference}]</v>
+&gt;[Point 2]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[Subtopic B description, \textit{italic reference}]</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>[related-file].pdf</v>
-      </c>
-      <c r="B3" t="str">
-        <v>[related-image].webp</v>
-      </c>
-      <c r="C3" t="str">
-        <v>[related-image].png</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>[related-file].pdf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[related-image].webp</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[related-image].png</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>[Research Area 2 Title]</v>
-      </c>
-      <c r="B1" t="str">
-        <v>[Subtopic]</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>[Research Area 2 Title]</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>[Subtopic]</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>[Research Area 2 description]</v>
-      </c>
-      <c r="B2" t="str">
-        <v>[Subtopic description, \href{https://example.com}{paper link}]</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>[Research Area 2 description]</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[Subtopic description, \href{https://example.com}{paper link}]</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>[file].pdf</v>
-      </c>
-      <c r="B3" t="str">
-        <v>[file2].pdf</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>[file].pdf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[file2].pdf</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>[Dataset/Model 1]</v>
-      </c>
-      <c r="B1" t="str">
-        <v>[Dataset/Model 2]</v>
-      </c>
-      <c r="C1" t="str">
-        <v>[Dataset/Model 3]</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>[Dataset/Model 1]</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>[Dataset/Model 2]</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>[Dataset/Model 3]</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>[Dataset 1 description]</v>
-      </c>
-      <c r="B2" t="str">
-        <v>[Dataset 2 description]</v>
-      </c>
-      <c r="C2" t="str">
-        <v>[Model 3 description]</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>[Dataset 1 description]</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[Dataset 2 description]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[Model 3 description]</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/网站内容_英文.xlsx
+++ b/网站内容_英文.xlsx
@@ -1,33 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Homepage" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Area 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Area 2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data &amp; Model" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Homepage" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
   <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,80 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -444,270 +396,160 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F7"/>
+  <cols>
+    <col min="1" max="1" width="35.83203125" customWidth="1"/>
+    <col min="2" max="2" width="60.83203125" customWidth="1"/>
+    <col min="3" max="3" width="50.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="5" max="5" width="60.83203125" customWidth="1"/>
+    <col min="6" max="6" width="30.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Basic Information</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Research Areas:</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Publication</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Course</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
+      <c r="A1" t="str">
+        <v>Basic Information</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Research</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Education</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Publication</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Project</v>
+      </c>
+      <c r="F1" t="str">
+        <v>News</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Desheng, Undergraduate, School of Foreign Languages, Shanghai Jiao Tong University</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Contrastive Linguistics: Japanese-Chinese contrastive research across phonological, lexical, and syntactic levels</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2022–Present, Shanghai Jiao Tong University, School of Foreign Languages, B.A.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Research on Script and Language Exchange in the Chinese Character Cultural Sphere, PRP Undergraduate Research Program, Participant (Supervisor: Prof. Li Siqi)</t>
-        </is>
+      <c r="A2" t="str">
+        <v>Desheng</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Contrastive Linguistics: Japanese-Chinese contrastive research across phonological, lexical, and syntactic levels</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2022–Present, Shanghai Jiao Tong University, School of Foreign Languages, B.A.</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v>Research on Script and Language Exchange in the Chinese Character Cultural Sphere, PRP Undergraduate Research Program, Participant (Supervisor: Prof. Li Siqi)</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>photo.jpg</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Cognitive Semantics: Media corpus research based on cognitive critical discourse analysis</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Sep 2025–Feb 2026, Osaka University, School of Foreign Studies, Exchange Student</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+      <c r="A3" t="str">
+        <v>Undergraduate</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Cognitive Semantics: Media corpus research based on cognitive critical discourse analysis</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Sep 2025–Feb 2026, Osaka University, School of Foreign Studies, Exchange Student</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>\href{https://www.sjtu.edu.cn}{School of Foreign Languages, Shanghai Jiao Tong University}</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>desheng@example.edu</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>photo.jpg</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>\href{https://github.com/wuyutanhongyuxin-cell}{GitHub}</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[Research Area 1 Title]</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>[Subtopic A]</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>[Subtopic B]</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>[Detailed description, use \textbf{bold} and \href{url}{links}]</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>[Subtopic A description]
-&gt;[Point 1]
-&gt;[Point 2]</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>[Subtopic B description, \textit{italic reference}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>[related-file].pdf</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>[related-image].webp</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>[related-image].png</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[Research Area 2 Title]</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>[Subtopic]</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>[Research Area 2 description]</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>[Subtopic description, \href{https://example.com}{paper link}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>[file].pdf</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>[file2].pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[Dataset/Model 1]</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>[Dataset/Model 2]</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>[Dataset/Model 3]</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>[Dataset 1 description]</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>[Dataset 2 description]</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>[Model 3 description]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+  </ignoredErrors>
 </worksheet>
 </file>